--- a/config/generated/templates/Character.xlsx
+++ b/config/generated/templates/Character.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="31">
   <si>
     <t>@table</t>
   </si>
@@ -34,21 +34,24 @@
     <t>id</t>
   </si>
   <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
+    <t>@groups</t>
+  </si>
+  <si>
+    <t>common</t>
   </si>
   <si>
     <t>@schema</t>
   </si>
   <si>
-    <t>d3c555eef7a03aaf</t>
+    <t>3af879f110f287a7</t>
   </si>
   <si>
     <t>#name</t>
   </si>
   <si>
+    <t>source_avatar_id</t>
+  </si>
+  <si>
     <t>rarity</t>
   </si>
   <si>
@@ -85,13 +88,16 @@
     <t>string</t>
   </si>
   <si>
-    <t>#scope</t>
+    <t>#groups</t>
   </si>
   <si>
     <t>#input</t>
   </si>
   <si>
     <t>key</t>
+  </si>
+  <si>
+    <t>range=1..2147483647</t>
   </si>
   <si>
     <t>range=4..5</t>
@@ -522,10 +528,11 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="23.7109375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" style="5" customWidth="1"/>
-    <col min="5" max="6" width="19.7109375" style="5" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" style="5" customWidth="1"/>
+    <col min="6" max="7" width="19.7109375" style="5" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -582,10 +589,13 @@
       <c r="G2" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="H2" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>5</v>
@@ -604,17 +614,20 @@
       </c>
       <c r="G3" s="5" t="s">
         <v>15</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>20</v>
@@ -626,12 +639,15 @@
         <v>22</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>7</v>
@@ -649,31 +665,37 @@
         <v>7</v>
       </c>
       <c r="G5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="5"/>
+        <v>27</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="E6" s="5"/>
-      <c r="F6" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="F6" s="5"/>
       <c r="G6" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -681,17 +703,22 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from 4 to 5." promptTitle="Integer range" prompt="Enter an integer from 4 to 5." sqref="C8:C1007">
+  <dataValidations count="4">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." sqref="C8:C1007">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from 4 to 5." promptTitle="Integer range" prompt="Enter an integer from 4 to 5." sqref="D8:D1007">
       <formula1>4</formula1>
       <formula2>5</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Destruction, Hunt, Erudition, Harmony, Nihility, Preservation, Abundance, Remembrance, Elation" promptTitle="CombatPath enum" prompt="Select a value from the dropdown." sqref="D8:D1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Destruction, Hunt, Erudition, Harmony, Nihility, Preservation, Abundance, Remembrance, Elation" promptTitle="CombatPath enum" prompt="Select a value from the dropdown." sqref="E8:E1007">
       <formula1>"Destruction,Hunt,Erudition,Harmony,Nihility,Preservation,Abundance,Remembrance,Elation"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Physical, Fire, Ice, Lightning, Wind, Quantum, Imaginary" promptTitle="CombatElement enum" prompt="Select a value from the dropdown." sqref="E8:E1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Physical, Fire, Ice, Lightning, Wind, Quantum, Imaginary" promptTitle="CombatElement enum" prompt="Select a value from the dropdown." sqref="F8:F1007">
       <formula1>"Physical,Fire,Ice,Lightning,Wind,Quantum,Imaginary"</formula1>
     </dataValidation>
   </dataValidations>
